--- a/Competition/Summer_2024/Liste des équipes.xlsx
+++ b/Competition/Summer_2024/Liste des équipes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jacob Turcotte\Documents\GitHub\CCI_UdeS\Competition\Summer_2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1C85C3-D2EE-4904-9895-D576FEDC8D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97985EF5-4F72-417F-8713-A588388DAF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1920" yWindow="1920" windowWidth="20304" windowHeight="12696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Liste d'équipe" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>Liste de participants:</t>
   </si>
@@ -132,12 +132,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -157,6 +151,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,150 +658,152 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="29">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="30"/>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="32">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="33"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="12"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="8">
         <v>2</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="9"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="11">
         <v>3</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="14">
         <v>3</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="21"/>
+      <c r="D7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="17">
         <v>4</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="24"/>
+      <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="20">
         <v>4</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="27"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="23">
         <v>5</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="30"/>
+      <c r="E10" s="24"/>
     </row>
     <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="26">
         <v>5</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="33"/>
+      <c r="E11" s="27"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D13">
